--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260929.xlsx
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,167,617</t>
+          <t>536,404</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,231,288</t>
+          <t>1,167,617</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>536,404</t>
+          <t>2,231,288</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>602,600</t>
+          <t>1,366,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,366,000</t>
+          <t>602,600</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>143,921</t>
+          <t>987,822</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>987,822</t>
+          <t>143,921</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>3,259,000</t>
+          <t>718,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>718,000</t>
+          <t>3,259,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>923,659</t>
+          <t>1,179,441</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,179,441</t>
+          <t>923,659</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>143,386</t>
+          <t>7,067,249</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>7,067,249</t>
+          <t>143,386</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>4,015,578</t>
+          <t>384,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>384,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>4,015,578</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,168,076</t>
+          <t>765,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>765,000</t>
+          <t>1,168,076</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>747,000</t>
+          <t>286,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>490,000</t>
+          <t>747,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>4,889,956</t>
+          <t>490,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>286,000</t>
+          <t>4,889,956</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>409,000</t>
+          <t>1,733,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,733,000</t>
+          <t>409,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>326,000</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>168,000</t>
+          <t>63,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>63,538</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>326,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
